--- a/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
+++ b/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
@@ -11,9 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_推計誤差" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_認定率と在宅サービス利用率の実績" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_当方の分析との突合" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_施設・居住系で進めない件の切り分け" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_自己点検" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_確認事項" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面の状態" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_推計方法の設定の現状" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_進めない件の切り分け" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_自己点検" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_確認事項" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,7 +68,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +105,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,6 +188,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -550,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -712,8 +725,35 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の画面の写し（7点）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>施策反映（施設・居住系サービス利用者数）の3区分、実績及び推計方法の設定、推計方法の設定（2点）、施設・居住系サービス利用率の変化の参考画面</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>先へ進めない件の切り分け</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>推計名「将来推計1」。ログインID W018320002。公表時点は「暫定版データ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>注1）①②はいずれも「本シートの操作方法」の3番目に、「将来推計」の「推計方法の設定」画面から伸びを選択するよう記されています。伸びを決めるための資料です。
 注2）③④の推計誤差は、前年9月の認定率・利用率を当年9月の第1号被保険者数に乗じて求めた推計値を、当年9月の実績値で除したものです。1.00を上回れば推計が実績を上回り、下回れば推計が実績を下回ります。
@@ -721,53 +761,38 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　4件に含まれていないもの</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>含まれていないもの</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>施設・居住系サービス利用者数の伸びを設定するための参考シート</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>今回のお問合せはこの画面のものである。①②に相当するシート（施設・居住系サービス利用者数の伸びのパターンの比較）が4件の中にない。別に出力できるかを確認いただきたい</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みに関する資料</t>
+          <t>施設・居住系サービス利用者数の伸びを設定するための参考シート</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.112（地域支援事業の量の見込み）に関わる。本件とは別に整理している</t>
+          <t>今回のお問合せはこの画面のものである。①②に相当するシート（施設・居住系サービス利用者数の伸びのパターンの比較）が4件の中にない。別に出力できるかを確認いただきたい</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -777,24 +802,39 @@
       <c r="A17" s="5" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>令和7年度のサービス利用者数の推計誤差</t>
+          <t>地域支援事業の量の見込みに関する資料</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>④は令和6年度のみである。③（認定者数）は令和6年度・令和7年度の2か年がある</t>
+          <t>確認事項No.112（地域支援事業の量の見込み）に関わる。本件とは別に整理している</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度のサービス利用者数の推計誤差</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>④は令和6年度のみである。③（認定者数）は令和6年度・令和7年度の2か年がある</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2171,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2566,20 +2606,43 @@
       <c r="A24" s="5" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>計画素案の見込量表の出所が判明した</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>画面に表示された施設・居住系7サービスの利用者数が、計画素案 第6章第2節1の表の値と照合できる範囲（16値）で完全に一致する</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節の見込量表は、どのスクリプトからも生成されていない直書きであり、出所を特定できていなかった</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>出所は見える化システムの将来推計の自然体推計値である。表頭の「R8実績」は、令和8年度の月報（4月から7月まで）から計算した実績見込み値であり、年度の実績ではない。注記を改めた（確認事項No.131）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>認定率の定義が当方と異なる</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>第1号被保険者の認定率は令和7年度20.84％</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>計画素案は認定率21.8％（令和7年度）としている</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>分子に第2号被保険者の認定者を含むかどうかが異なる。計画に掲げる認定率の定義を1つに揃える</t>
         </is>
@@ -2603,7 +2666,1289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>画面の写しから確かめたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="66" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年9月11日に受領した画面の写し7点から読み取った内容。推計名「将来推計1」、ログインID W018320002（保険者番号01832）、公表時点は「暫定版データ」。画面上部の保険料額（月額・暫定値）は第10期6,179円・令和12年度7,002円である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　左のナビゲーションの順序と到達の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の概要</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>到達済</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>推計の開始と保存</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>到達済</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>実績及び推計方法の設定</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>到達済</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>施策反映　認定者数</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>到達済</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>施策反映　施設・居住系サービス利用者数</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>現在地</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>施策反映　在宅サービス利用者数等</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>未到達</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>「次の施策反映へ」はこの画面へ進むボタンである</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業の見込み量推計</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>未到達</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>保険料額の算定</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>未到達</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>推計結果概要の確認</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>未到達</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>都道府県への提出</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>未到達</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>注1）施策反映は「認定者数」→「施設・居住系サービス利用者数」→「在宅サービス利用者数等」の順です。現在地は2番目で、「次の施策反映へ」は3番目へ進むボタンです。
+注2）未到達は5件です。保険料額の算定と都道府県への提出はこの先にあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2　施策反映（施設・居住系サービス利用者数）の画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>区分（画面の選択）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>収録サービス</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>画面に表示された値</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービス</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>R6 60／R7 64／R8 66／R9 66／R10 68／R11 68／R12 69／R17 73／R22 75／R27 72／R32 71</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>R6 85／R7 82／R8 79／R9 79</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>R6 0／R7 0／R8 0／R9 0</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>全年度0。区域内に事業所がなく、推計誤差も算定されていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>R6 58／R7 60／R8 65</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>R6 146／R7 140／R8 146／R9 146</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>R6 137／R7 130／R8 111／R9 111</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>R6 6／R7 6／R8 7</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>7サービス</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr"/>
+      <c r="E28" s="18" t="inlineStr"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>注3）区分は「居宅サービス」「地域密着型サービス」「施設サービス」の3つで、画面のドロップダウンで切り替えます。合わせて7サービスです。
+注4）介護療養型医療施設は画面にありません（令和6年3月末で廃止済み）。当方が先に切り分けの候補に挙げた「介護療養型医療施設の欄が残っていないか」は該当しません。
+注5）地域密着型特定施設入居者生活介護は全年度0で表示されており、空欄ではありません。当方が先に見込みを「高い」とした「実績のないサービスの欄が空でないか」も該当しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>3　画面の表に並ぶ年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>西暦</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>入力の対象（令和9年度以降）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>注6）**見える化システムは令和32年度（2050年度）まで推計します。**中長期の年度はR12・R17・R22・R27・R32の5か年です。
+注7）当方は確認事項No.114で「令和22年度までの中長期推計」をお諮りしていましたが、システムは令和32年度まで持っています。算定の範囲を令和32年度まで広げられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>4　無効（グレー）になっていたボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ボタン</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>本来の働き</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>無効であることの読み方</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>次の施策反映へ</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>在宅サービス利用者数等の画面へ進む</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>今回のお問合せの対象</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>自然体推計に全て戻す</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>施策反映で変更した値を自然体推計の値に戻す</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>変更した値が1つもないため無効になっていると読める。画面の値はすべて自然体推計のままである</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>保険料額の更新</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>入力を反映して保険料額を計算し直す</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>同上。更新すべき変更がない</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>注8）3つとも無効である点が手がかりです。「自然体推計に全て戻す」と「保険料額の更新」は、値を1つも変更していないときに無効になるボタンです。「次の施策反映へ」も同じ条件で無効になっている可能性があります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>推計方法の設定の現状と当方の方針との差</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="66" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>「実績及び推計方法の設定」は3項目とも「初期設定済です」と表示されており、既定値のままである。既定値と当方の方針には差がある。画面上部の保険料額（第10期 月額6,179円）はこの既定値による自然体推計の値である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　「実績及び推計方法の設定」の3項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>既定値（画面の記載）</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>当方の方針との差</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>総人口と被保険者数の設定</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>国立社会保障・人口問題研究所「日本の地域別将来推計人口（令和5（2023）年推計）」（公表値又は補正値）が初期値</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>当方は案C（総人口＝地方創生総合戦略、年齢階級別＝住民基本台帳の実績趨勢）を採っている（令和8年9月10日 発注者了承）。社人研推計との差は3町計 令和11年度の65歳以上で100人である。設定を変えないと案Cが反映されない</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>No.127</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告の設定</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度年報及び令和7年度、8年度の最新の月報が初期値</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>令和8年度は令和8年4月から7月までの4か月の月報である。当方は数量の基準年度を令和7年度のみとしている</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>No.128</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>推計方法の設定</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>実績値としては令和8年度が初期値</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>実績値が令和8年度に置かれている。当方の採用パターンP3は令和7年度を基準年度としている</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>No.128</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2　「推計方法の設定」の画面で読み取れた設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>設定項目</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>現在の値</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>当方の見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>（3）1）令和8年度の施設・居住系サービス利用者数の実績見込み値</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>編集していない</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>編集しない場合は令和8年度の介護保険事業状況報告月報の値から計算した実績見込み値（計算値）を使用する</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>編集しない場合は令和8年度（4か月）の月報から計算した値になる。編集すれば令和7年度の水準に置き換えられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>（3）2）施設・居住系サービスの自然体推計に用いる利用率等の伸び</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>0（ゼロ）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>選択式</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>伸びを0と置くことは、利用率が令和8年度の水準のまま動かないと置くことである。受領した①②の参考シートは、この選択を決めるための資料である</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>（4）1）令和8年度の在宅サービス利用者数の実績見込み値</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>編集していない</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>編集しない場合は令和8年度の月報の値から計算した実績見込み値を使用する</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>編集しない場合は令和8年度（4か月）の月報から計算した値になる。編集すれば令和7年度の水準に置き換えられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>（4）2）令和8年度の在宅サービス利用回（日）数の実績見込み値</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>編集していない</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>編集しない場合は令和8年度（4か月）の月報から計算した値になる。編集すれば令和7年度の水準に置き換えられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>（4）3）在宅サービス利用者数の自然体推計に用いる利用率の伸び</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>0（ゼロ）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>選択式</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>伸びを0と置くことは、利用率が令和8年度の水準のまま動かないと置くことである。受領した①②の参考シートは、この選択を決めるための資料である</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>（4）4）在宅サービス1人1月あたり利用回（日）数の自然体推計に用いる伸び</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>0（ゼロ）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>選択式</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>伸びを0と置くことは、利用率が令和8年度の水準のまま動かないと置くことである。受領した①②の参考シートは、この選択を決めるための資料である</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>注1）伸びの選択が0（ゼロ）のものが3件、令和8年度の実績見込み値を編集していないものが3件です。
+注2）したがって、画面の保険料額 第10期 月額6,179円は「令和8年度（4月から7月までの4か月）の実績見込み値を基礎に、伸びをすべて0と置いた」推計です。
+注3）当方の採用パターンP3（令和7年度基準・認定者数の伸びのみ反映）は算定上の月額基準額6,428円、現行P1（見える化の自然体推計×案C補正）は6,740円です。いずれとも置き方が異なります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>3　施設・居住系サービス利用率の伸びの選択肢</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度を含むか</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>当該市町村における令和3年度→令和8年度の伸び</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>含む</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>当該市町村における令和7年度→令和8年度の伸び</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>含む</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>当該市町村における令和6年度→令和8年度の伸び</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>含む</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>当該市町村における令和6年度→令和7年度の伸び</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>含まない</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>注4）この画面は「参考情報」ボタンから開きます（施設・居住系サービス利用率の変化。S212000_init.action）。当方が確認事項No.124で「施設・居住系の参考シートがない」とお尋ねしたのは誤りでした。画面から開けます。
+注5）④だけが令和8年度を含みません。令和8年度は4か月であり夏季に偏るため、④を選ぶことが当方の整理と合います。ただし1年分の伸びを延長することになります。
+注6）①（令和3年度→令和8年度）の伸びは施設・居住系の3サービスとも0.0％です。施設・居住系は利用率が動いておらず、伸びを0と置いても大きくは変わりません。在宅は居宅療養管理指導が令和3年度4.97％から令和8年度14.22％へ2.9倍になっており、扱いが異なります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2623,414 +3968,514 @@
     <row r="2" ht="66" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>当方は見える化システムに接続できないため、画面の状態を確認できない。受領資料から分かることを根拠に、確かめる順序を示す。原因を特定したものではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>確かめること</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>根拠（受領資料から分かること）</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+          <t>画面の写しにより、先にお示しした切り分けのうち2件は該当しないことが分かった。残る見方を示す。当方はシステムを操作できないため原因を特定したものではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　先にお示しした切り分けの結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>先にお示しした見方</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>画面の写しから分かること</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>実績のないサービスの欄が空でないか</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護は全年度0で表示されており、空欄ではない</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>介護療養型医療施設の欄が残っていないか</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>画面に当該区分はない（令和6年3月末で廃止済み）</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>前の段階の設定が確定しているか</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>「実績及び推計方法の設定」は3項目とも「初期設定済です」と表示されており、設定自体は済んでいる</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>該当しない見込み</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>定員との整合の検査に掛かっていないか</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>画面に定員の入力欄は見当たらない。ただし地域密着型介護老人福祉施設入所者生活介護は令和8年度65人で、当方が把握している定員62人を上回る</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>なお確かめる</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>入力値の形式が誤っていないか</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>値はすべて自然体推計のままで、入力した形跡がない</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>該当しない見込み</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>画面側の問題でないか</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>写しからは判断できない</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>なお確かめる</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>システム側の不具合でないか</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>写しからは判断できない</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>なお確かめる</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2　画面の写しから新たに考えられること</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>考えられること</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>確かめ方</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>見込み</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="7" t="n">
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>実績のないサービスの欄が空でないか</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>当広域連合では地域密着型特定施設入居者生活介護の推計誤差が算定されていない（実績がないため）。施設・居住系7区分のうちこの1件だけが「―」である</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>施設・居住系の画面で、地域密着型特定施設入居者生活介護の欄が空欄になっていないかを見る。空欄であれば0を入力する</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>値を1つも変更していないため無効になっている</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>「自然体推計に全て戻す」と「保険料額の更新」も同時に無効である。この2つは値を変更していないときに無効になるボタンであり、「次の施策反映へ」も同じ条件で無効になっている可能性がある</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度以降のいずれかのセルに値を入力してみる（自然体推計と同じ値でよい）。入力後に3つのボタンが有効になるかを見る</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>高い</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="n">
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>介護療養型医療施設の欄が残っていないか</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>受領した推計誤差の一覧に介護療養型医療施設はない（令和6年3月末で廃止済み）。画面に区分が残っている場合は入力を求められる可能性がある</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>画面に当該区分があれば0を入力する</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>3つの区分をすべて表示していない</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>区分は居宅サービス・地域密着型サービス・施設サービスの3つある。写しでは3区分とも表示されているが、同じ操作の流れの中で3区分を順に開いたかは写しからは分からない</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ドロップダウンで3区分を順に開き直したうえでボタンを見る</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="n">
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>前の段階の設定が確定しているか</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>受領した4件はいずれも「推計方法の設定」画面で認定率の伸び・在宅サービス利用率の伸びを選ぶための資料である。この2つの設定を求められている状況であることを示す</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>認定率の伸びと在宅サービス利用率の伸びが選択済み・保存済みかを確認する。未選択のまま先の画面に入っていると戻される場合がある</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>高い</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>表を最後の行まで表示していない</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービスと施設サービスの表は令和9年度の途中までしか写っておらず、表の右側にスクロールバーがある。居宅サービスは令和32年度まで表示されている</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>各区分の表を令和32年度の行まで下へ送ってからボタンを見る</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>定員との整合の検査に掛かっていないか</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>施設・居住系は必要利用定員総数と結びつく。当区域は認知症対応型共同生活介護の定員が未確定である（99人＋［要確認］。確認事項No.88）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>定員の入力欄があるか、入力した利用者数が定員を超えていないかを見る</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>画面の下部に未入力の欄がある</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>写しは画面の一部であり、下部に別の入力欄があるかは分からない</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>画面を最下部まで送り、空欄がないかを目視する</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>入力値の形式が誤っていないか</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>全角数字・小数点・空白・負の値・カンマの混入を見る。特に他の表から貼り付けた場合に起きやすい</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="7" t="n">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>注1）見込みを「高い」としたのは、無効になっているボタン3つのうち2つが「値を変更していないときに無効になる」性質のものだからです。
+注2）それでも解消しない場合は、見える化システムのヘルプデスクへ照会してください。保険者番号01832・推計名「将来推計1」・画面名（施設・居住系サービス利用者数の施策反映）・操作手順を添えると早いと思われます。
+注3）当方は mieruka.mhlw.go.jp に接続できないため、上記は画面の写しから言えることにとどまります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>3　画面の利用者数と当方が把握している定員</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>160人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>画面側の問題でないか</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>別のブラウザで試す。セッションが切れていないか（一定時間放置していないか）を見る。未入力の欄に自動で移動しない場合は、画面を上から順に空欄がないか目視する</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>低い</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="D27" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>システム側の不具合でないか</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>上記で解消しない場合は、見える化システムのヘルプデスクへ照会する。保険者番号01832・該当画面名・操作手順・入力済みの値を添えると早い</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>注1）当方は mieruka.mhlw.go.jp に接続できないため、画面の挙動を確かめられません。上記は受領資料から言えることにとどまります。
-注2）1と3の見込みを「高い」としたのは、当区域に実績のないサービスが施設・居住系に1件あること、及び今回お送りいただいた4件がいずれも前段の設定（認定率・在宅サービス利用率の伸び）の資料であることによります。
-注3）画面の状態が分かる資料（画面の写し、エラーの表示、入力済みの値）をいただければ、さらに絞り込めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>参考　施設・居住系7区分の状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>サービス</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>推計誤差（基本推計）</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>定員</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>介護老人福祉施設</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>1.0296</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>160人</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>北海道 特別養護老人ホーム名簿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>介護老人保健施設</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0.9261</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>［要確認］</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>区域内の施設の定員を未受領</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>介護医療院</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>1.1664</v>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr">
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>1.0949</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C28" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>156人</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧。混合型か介護専用型かは未確認（確認事項No.113）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr">
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
-        <v>1.0827</v>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="C29" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>99人＋［要確認］</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>くるみの郷（東川町）の定員が未確定（確認事項No.88）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>―（実績なし）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>区域内に事業所がない</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>―（事業所なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>1.0303</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C31" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>62人</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>北海道 特別養護老人ホーム名簿</t>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>注4）地域密着型介護老人福祉施設入所者生活介護は令和8年度65人で、当方が把握している定員62人を上回ります。画面の値は月平均の利用者数であり、空床型の短期入所等を含むことがあるため、直ちに定員超過を意味するものではありません。定員の確認とあわせて整理を要します。
+注5）介護老人保健施設は令和7年度130人から令和8年度111人へ14.6％減っています。令和8年度は4か月の月報によるものです。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3089,7 +4534,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>受領したファイルの件数が4件であること</t>
+          <t>受領した資料の件数が5件であること（9月11日の4ファイルと画面の写し）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3099,7 +4544,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>5件</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -3427,12 +4872,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>切り分けの各項目に確かめ方が示されていること</t>
+          <t>新たに考えられることの各項目に確かめ方が示されていること</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -3447,32 +4892,188 @@
       </c>
       <c r="F18" s="5" t="inlineStr"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="18" t="inlineStr"/>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>画面の区分と収録サービスが施設・居住系7区分と一致すること</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>画面 7サービス／推計誤差の一覧 7サービス</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>画面で全年度0のサービスが、推計誤差の算定されていないものと一致すること</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>画面で全年度0 1件</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>画面の年度に中長期の年度が含まれること</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>画面の年度 R6・R7・R8・R9・R10・R11・R12・R17・R22・R27・R32</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>中長期はR12・R17・R22・R27・R32</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>推計方法の設定のうち伸びの選択がすべて0（ゼロ）であること</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>選択式の項目</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>0（ゼロ）3件／選択式3件</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>計画素案の見込量表の値が画面の自然体推計値と一致すること</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>照合できた16値</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>無効になっていたボタンが3件で、うち2件が値の変更に依存するものであること</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>次の施策反映へ・自然体推計に全て戻す・保険料額の更新</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="18" t="inlineStr"/>
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>14件</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>適合14件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>20件</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>適合20件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>注1）収録値は受領したファイルから読み取った当広域連合の行のみです。全国の他の保険者の値は収録していません。
 注2）1件でも不適合があると、本表を作るスクリプトは終了コード1で終わります。</t>
@@ -3482,20 +5083,20 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3588,23 +5189,23 @@
     <row r="6" ht="140" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>No.124</t>
+          <t>No.127</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>認定率（①）と在宅サービス利用率（②）については伸びのパターンを比較する参考シートが出力されているが、施設・居住系サービス利用者数について同じ形のシートが受領資料に含まれていない。見える化システムから出力できるものであればご提供いただきたい。施設・居住系は定員に縛られ、在宅とは伸びの置き方が異なるため、実績の推移を確かめたうえで伸びを選ぶ必要がある。</t>
+          <t>「実績及び推計方法の設定」の「総人口と被保険者数の設定」は「初期設定済です」と表示されており、国立社会保障・人口問題研究所「日本の地域別将来推計人口（令和5（2023）年推計）」が初期値として登録されている。当方は令和8年9月10日のご了承により案C（総人口＝地方創生総合戦略、年齢階級別＝住民基本台帳の実績趨勢）を採っており、3町計 令和11年度の65歳以上は案C 9,213人・見える化A系列（社人研）9,313人で100人の差がある。システムの設定を案Cに改めないと、計画本文の人口とシステムの推計が食い違う。設定を改めてよいか、また補正値の入力を当方で用意してよいかご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節・第4節</t>
+          <t>将来推計 第1段階
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3621,82 +5222,180 @@
     <row r="7" ht="140" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>No.128</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値を編集するか</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>「推計方法の設定」では、施設・居住系サービス及び在宅サービスの令和8年度の実績見込み値について「編集しない場合は令和8年度の介護保険事業状況報告月報の値から計算した実績見込み値（計算値）を使用します」とされており、現在は編集していない。令和8年度は令和8年4月から7月までの4か月であり、当方は数量の基準年度を令和7年度のみとしている。また在宅サービスは冬季が夏季より2.48％低いため、4月から7月までの値は夏季に偏る。①実績見込み値を編集して令和7年度の水準に置き換えるか、②月報からの計算値のままとするかをご判断いただきたい。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階
+サービス見込量 第1次概算</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>No.129</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>「推計方法の設定」の伸びの選択は、施設・居住系サービスの利用率等の伸び、在宅サービス利用者数の利用率の伸び、在宅サービス1人1月あたり利用回（日）数の伸びの3つとも「0（ゼロ）」である。受領した参考シート（認定率・在宅サービス利用率）と画面の「参考情報」（施設・居住系サービス利用率の変化）は、この選択を決めるための資料である。施設・居住系は①令和3年度→令和8年度・②令和7年度→令和8年度・③令和6年度→令和8年度・④令和6年度→令和7年度の4つから選ぶ。①から③は令和8年度（4か月）を含むため、当方の整理では④が合う。ただし1年分の伸びを延長することになる。なお①（令和3年度→令和8年度）の伸びは施設・居住系の3サービスとも0.0％であり、施設・居住系については伸びを0と置いても大きくは変わらない。在宅は居宅療養管理指導が令和3年度4.97％から令和8年度14.22％へ2.9倍になっており、扱いが異なる。伸びの選択をご判断いただきたい。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階
+サービス見込量 第1次概算</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>No.124</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無（画面の写しにより解決）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>認定率（①）と在宅サービス利用率（②）については伸びのパターンを比較する参考シートが出力されているが、施設・居住系サービス利用者数について同じ形のシートが受領資料に含まれていない。見える化システムから出力できるものであればご提供いただきたい。施設・居住系は定員に縛られ、在宅とは伸びの置き方が異なるため、実績の推移を確かめたうえで伸びを選ぶ必要がある。【解決】令和8年9月11日に受領した画面の写しにより、施設・居住系についても「参考情報」ボタンから「施設・居住系サービス利用率の変化」の画面が開けることが分かった（S212000_init.action）。当方のお尋ねは誤りであった。伸びの選択は確認事項No.129で扱う。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>―（解決）</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>No.125</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>計画に掲げる認定率の定義を揃えること</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>受領した認定率のシートでは、第1号被保険者の認定率は令和7年度20.84％である。一方、計画素案は認定率21.8％（令和7年度）としている。差は分子に第2号被保険者の認定者を含むかどうかによると考えられる。①計画に掲げる認定率を、第1号被保険者のみとするか、第2号被保険者を含むかを決めていただきたい。②見える化システムで推計する場合は同システムの定義に従うことになるため、計画本文の値と食い違わないよう揃える必要がある。③時点も異なる（受領資料は各年9月末、当方は年度末）。</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節3・第6章第1節
 将来推計 第1段階・第2段階</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="140" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>No.126</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>推計方式は基本推計でよいか</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>受領した認定者数の推計誤差では、令和6年度は基本推計▲0.72％・包括推計＋0.55％、令和7年度は基本推計▲0.50％・包括推計＋1.91％である。令和6年度だけを見れば包括推計の方が1.00に近いが、基本推計は2か年とも実績をわずかに下回る側で振れが小さく（2か年平均0.61％）、包括推計は2か年とも上回る側で振れが大きい（同1.23％）。当方の採用パターンP3は年齢階級別の人口に階級別認定率を乗じる方法であり、基本推計に近い。見える化システムで推計方式を選ぶ場面では基本推計を選ぶ整理でよいか。</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>将来推計 第2段階
 サービス見込量 第1次概算</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>注1）本表により新たに起票した確認事項は4件（No.123〜No.126）です。
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>注1）本表により起票した確認事項は7件（No.123〜No.129）です。うちNo.124は画面の写しにより解決しました。
 注2）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。計画素案の本文には注記しません。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
